--- a/linear_regression_dataset_spreadsheet.xlsx
+++ b/linear_regression_dataset_spreadsheet.xlsx
@@ -716,7 +716,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/datasets/aungpyaeap/fish-market</t>
+          <t>https://www.kaggle.com/datasets/vipullrathod/fish-market</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
